--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -958,7 +958,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -331,7 +331,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -363,7 +363,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -379,7 +379,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -502,7 +502,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -873,7 +873,7 @@
 【JP Core仕様】頓用指示時にはJAMI処方・注射オーダ標準用法規格の表6 イベント区分、イベント詳細区分(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionJAMI_CS”)を推奨するが、MERIT-9 処方オーダ 表5 頓用指示(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionMERIT9_CS”) を使用してもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS|1.1.0a</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -921,7 +921,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -942,7 +942,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1033,7 +1033,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1054,7 +1054,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1109,7 +1109,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1144,7 +1144,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -1304,7 +1304,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -1358,7 +1358,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1380,7 +1380,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -1389,7 +1389,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1410,7 +1410,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -1448,7 +1448,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1458,7 +1458,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1831,7 +1831,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1846,7 +1846,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -331,7 +331,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
 </t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
 </t>
   </si>
   <si>
@@ -363,7 +363,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
 </t>
   </si>
   <si>
@@ -379,7 +379,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -502,7 +502,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
 </t>
   </si>
   <si>
@@ -873,7 +873,7 @@
 【JP Core仕様】頓用指示時にはJAMI処方・注射オーダ標準用法規格の表6 イベント区分、イベント詳細区分(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionJAMI_CS”)を推奨するが、MERIT-9 処方オーダ 表5 頓用指示(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionMERIT9_CS”) を使用してもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -921,7 +921,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -942,7 +942,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
 </t>
   </si>
   <si>
@@ -1033,7 +1033,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1054,7 +1054,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
 </t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1109,7 +1109,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
 </t>
   </si>
   <si>
@@ -1144,7 +1144,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -1304,7 +1304,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -1358,7 +1358,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
 </t>
   </si>
   <si>
@@ -1380,7 +1380,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -1389,7 +1389,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1410,7 +1410,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity|4.0.1}</t>
+RangeQuantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -1448,7 +1448,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -1458,7 +1458,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1831,7 +1831,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.42578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1846,7 +1846,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
